--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486906_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486906_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.0185</v>
+        <v>7.9906</v>
       </c>
       <c r="E2" t="n">
-        <v>5.7202</v>
+        <v>5.9294</v>
       </c>
       <c r="F2" t="n">
-        <v>2.2983</v>
+        <v>2.0612</v>
       </c>
       <c r="G2" t="n">
         <v>5.4597</v>
@@ -610,13 +610,13 @@
         <v>2.0534</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.0573</v>
+        <v>-0.0852</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.07770000000000001</v>
+        <v>0.1315</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0204</v>
+        <v>-0.2167</v>
       </c>
       <c r="V2" t="n">
         <v>0.768</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.2177</v>
+        <v>4.8</v>
       </c>
       <c r="E3" t="n">
-        <v>6.4306</v>
+        <v>6.9536</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.2129</v>
+        <v>-2.1536</v>
       </c>
       <c r="G3" t="n">
         <v>1.3477</v>
@@ -688,13 +688,13 @@
         <v>1.8481</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.7973</v>
+        <v>-0.215</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.4961</v>
+        <v>0.0269</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3012</v>
+        <v>-0.2419</v>
       </c>
       <c r="V3" t="n">
         <v>3.2566</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.4418</v>
+        <v>3.3198</v>
       </c>
       <c r="E4" t="n">
-        <v>2.7103</v>
+        <v>2.2919</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7315</v>
+        <v>1.0279</v>
       </c>
       <c r="G4" t="n">
         <v>1.813</v>
@@ -766,13 +766,13 @@
         <v>1.4374</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.6587</v>
+        <v>-0.7806999999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0854</v>
+        <v>-0.5038</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.5733</v>
+        <v>-0.2769</v>
       </c>
       <c r="V4" t="n">
         <v>1.8768</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P. CAMPENY LLOVERAS</t>
+          <t>J. TAVELLI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.429</v>
+        <v>2.7568</v>
       </c>
       <c r="E5" t="n">
-        <v>1.0607</v>
+        <v>3.0261</v>
       </c>
       <c r="F5" t="n">
-        <v>1.3683</v>
+        <v>-0.2693</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4173</v>
+        <v>3.1731</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3147</v>
+        <v>0.363</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1027</v>
+        <v>2.8101</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8167</v>
+        <v>3.2935</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6458</v>
+        <v>0.1363</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1709</v>
+        <v>3.1573</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.3993</v>
+        <v>-0.1204</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.3311</v>
+        <v>0.2268</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.0682</v>
+        <v>-0.3472</v>
       </c>
       <c r="P5" t="n">
-        <v>1.0267</v>
+        <v>0.8214</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.0267</v>
+        <v>0.8214</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9849</v>
+        <v>-0.0591</v>
       </c>
       <c r="T5" t="n">
-        <v>0.244</v>
+        <v>-0.2674</v>
       </c>
       <c r="U5" t="n">
-        <v>0.7409</v>
+        <v>0.2084</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-1.1786</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. TAVELLI</t>
+          <t>A. DUVAL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.3227</v>
+        <v>1.998</v>
       </c>
       <c r="E6" t="n">
-        <v>2.5031</v>
+        <v>2.8605</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.1803</v>
+        <v>-0.8625</v>
       </c>
       <c r="G6" t="n">
-        <v>3.1731</v>
+        <v>3.0023</v>
       </c>
       <c r="H6" t="n">
-        <v>0.363</v>
+        <v>-0.4443</v>
       </c>
       <c r="I6" t="n">
-        <v>2.8101</v>
+        <v>3.4466</v>
       </c>
       <c r="J6" t="n">
-        <v>3.2935</v>
+        <v>3.7595</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1363</v>
+        <v>0.221</v>
       </c>
       <c r="L6" t="n">
-        <v>3.1573</v>
+        <v>3.5385</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.1204</v>
+        <v>-0.7572</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2268</v>
+        <v>-0.6653</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.3472</v>
+        <v>-0.092</v>
       </c>
       <c r="P6" t="n">
-        <v>0.8214</v>
+        <v>-0.4107</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.4374</v>
       </c>
       <c r="R6" t="n">
-        <v>0.8214</v>
+        <v>1.0267</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.4931</v>
+        <v>0.5153</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.7905</v>
+        <v>0.5385</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2973</v>
+        <v>-0.0232</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.1786</v>
+        <v>-1.1088</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.1786</v>
+        <v>-1.1088</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. DUVAL</t>
+          <t>P. CAMPENY LLOVERAS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.0747</v>
+        <v>1.7734</v>
       </c>
       <c r="E7" t="n">
-        <v>3.1744</v>
+        <v>0.6422</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.0996</v>
+        <v>1.1312</v>
       </c>
       <c r="G7" t="n">
-        <v>3.0023</v>
+        <v>0.4173</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4443</v>
+        <v>0.3147</v>
       </c>
       <c r="I7" t="n">
-        <v>3.4466</v>
+        <v>0.1027</v>
       </c>
       <c r="J7" t="n">
-        <v>3.7595</v>
+        <v>0.8167</v>
       </c>
       <c r="K7" t="n">
-        <v>0.221</v>
+        <v>0.6458</v>
       </c>
       <c r="L7" t="n">
-        <v>3.5385</v>
+        <v>0.1709</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.7572</v>
+        <v>-0.3993</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.6653</v>
+        <v>-0.3311</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.092</v>
+        <v>-0.0682</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.4107</v>
+        <v>1.0267</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.4374</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>1.0267</v>
       </c>
       <c r="S7" t="n">
-        <v>0.592</v>
+        <v>0.3294</v>
       </c>
       <c r="T7" t="n">
-        <v>0.8522999999999999</v>
+        <v>-0.1744</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2603</v>
+        <v>0.5038</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.1088</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.1088</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.9016</v>
+        <v>0.7281</v>
       </c>
       <c r="E8" t="n">
-        <v>1.1342</v>
+        <v>0.8204</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7674</v>
+        <v>-0.0922</v>
       </c>
       <c r="G8" t="n">
         <v>0.4167</v>
@@ -1078,13 +1078,13 @@
         <v>1.2321</v>
       </c>
       <c r="S8" t="n">
-        <v>2.298</v>
+        <v>1.1246</v>
       </c>
       <c r="T8" t="n">
-        <v>1.0227</v>
+        <v>0.7088</v>
       </c>
       <c r="U8" t="n">
-        <v>1.2754</v>
+        <v>0.4158</v>
       </c>
       <c r="V8" t="n">
         <v>0.4189</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5974</v>
+        <v>0.6567</v>
       </c>
       <c r="E9" t="n">
         <v>-0.0659</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6633</v>
+        <v>0.7226</v>
       </c>
       <c r="G9" t="n">
         <v>0.4184</v>
@@ -1156,13 +1156,13 @@
         <v>0.2053</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0263</v>
+        <v>0.0329</v>
       </c>
       <c r="T9" t="n">
         <v>-0.0659</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0395</v>
+        <v>0.0988</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2328</v>
+        <v>0.2625</v>
       </c>
       <c r="E10" t="n">
         <v>-0.0659</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2987</v>
+        <v>0.3283</v>
       </c>
       <c r="G10" t="n">
         <v>0.2789</v>
@@ -1234,13 +1234,13 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0461</v>
+        <v>-0.0165</v>
       </c>
       <c r="T10" t="n">
         <v>-0.0659</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0198</v>
+        <v>0.0494</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.0115</v>
+        <v>-1.6697</v>
       </c>
       <c r="E11" t="n">
-        <v>0.743</v>
+        <v>0.8476</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.7545</v>
+        <v>-2.5174</v>
       </c>
       <c r="G11" t="n">
         <v>0.3466</v>
@@ -1312,13 +1312,13 @@
         <v>0.616</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3766</v>
+        <v>-0.0349</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2558</v>
+        <v>-0.1512</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1208</v>
+        <v>0.1163</v>
       </c>
       <c r="V11" t="n">
         <v>-2.5975</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.3564</v>
+        <v>-3.3721</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.7999</v>
+        <v>-3.9045</v>
       </c>
       <c r="F12" t="n">
-        <v>0.4434</v>
+        <v>0.5323</v>
       </c>
       <c r="G12" t="n">
         <v>-4.7024</v>
@@ -1390,13 +1390,13 @@
         <v>1.6427</v>
       </c>
       <c r="S12" t="n">
-        <v>0.346</v>
+        <v>0.3303</v>
       </c>
       <c r="T12" t="n">
-        <v>0.4879</v>
+        <v>0.3833</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.142</v>
+        <v>-0.0531</v>
       </c>
       <c r="V12" t="n">
         <v>0.5893</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.5365</v>
+        <v>-5.9123</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.8553</v>
+        <v>-4.6461</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.6812</v>
+        <v>-1.2662</v>
       </c>
       <c r="G13" t="n">
         <v>-3.7756</v>
@@ -1468,13 +1468,13 @@
         <v>1.4374</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.7773</v>
+        <v>-0.1531</v>
       </c>
       <c r="T13" t="n">
-        <v>0.0618</v>
+        <v>0.271</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.8391</v>
+        <v>-0.4241</v>
       </c>
       <c r="V13" t="n">
         <v>0.0698</v>
@@ -1504,10 +1504,10 @@
         <v>13.3318</v>
       </c>
       <c r="E14" t="n">
-        <v>14.6895</v>
+        <v>14.6893</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.3576</v>
+        <v>-1.3577</v>
       </c>
       <c r="G14" t="n">
         <v>8.195699999999995</v>
@@ -1522,7 +1522,7 @@
         <v>17.9486</v>
       </c>
       <c r="K14" t="n">
-        <v>2.177499999999998</v>
+        <v>2.1775</v>
       </c>
       <c r="L14" t="n">
         <v>15.7711</v>
@@ -1537,7 +1537,7 @@
         <v>-7.2994</v>
       </c>
       <c r="P14" t="n">
-        <v>2.053400000000001</v>
+        <v>2.0534</v>
       </c>
       <c r="Q14" t="n">
         <v>-11.2938</v>
@@ -1546,13 +1546,13 @@
         <v>13.3472</v>
       </c>
       <c r="S14" t="n">
-        <v>0.9881999999999999</v>
+        <v>0.988</v>
       </c>
       <c r="T14" t="n">
-        <v>0.8313999999999999</v>
+        <v>0.8314</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1566000000000002</v>
+        <v>0.1565999999999999</v>
       </c>
       <c r="V14" t="n">
         <v>2.0945</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.2718</v>
+        <v>5.4715</v>
       </c>
       <c r="E15" t="n">
-        <v>6.4589</v>
+        <v>5.7266</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.1871</v>
+        <v>-0.2551</v>
       </c>
       <c r="G15" t="n">
         <v>6.1556</v>
@@ -1624,13 +1624,13 @@
         <v>1.8481</v>
       </c>
       <c r="S15" t="n">
-        <v>1.3572</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>0.9141</v>
+        <v>0.1819</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4431</v>
+        <v>0.3751</v>
       </c>
       <c r="V15" t="n">
         <v>-0.008999999999999999</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.5782</v>
+        <v>3.9966</v>
       </c>
       <c r="E16" t="n">
         <v>6.0019</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.4237</v>
+        <v>-2.0053</v>
       </c>
       <c r="G16" t="n">
         <v>3.0861</v>
@@ -1702,13 +1702,13 @@
         <v>0.616</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.124</v>
+        <v>0.2944</v>
       </c>
       <c r="T16" t="n">
         <v>0.1936</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3176</v>
+        <v>0.1008</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.0887</v>
+        <v>1.0321</v>
       </c>
       <c r="E17" t="n">
-        <v>2.0465</v>
+        <v>1.1051</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0421</v>
+        <v>-0.073</v>
       </c>
       <c r="G17" t="n">
         <v>-0.9175</v>
@@ -1780,13 +1780,13 @@
         <v>1.8481</v>
       </c>
       <c r="S17" t="n">
-        <v>2.0193</v>
+        <v>0.9628</v>
       </c>
       <c r="T17" t="n">
-        <v>1.1853</v>
+        <v>0.2439</v>
       </c>
       <c r="U17" t="n">
-        <v>0.834</v>
+        <v>0.7189</v>
       </c>
       <c r="V17" t="n">
         <v>1.1922</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4291</v>
+        <v>0.7569</v>
       </c>
       <c r="E18" t="n">
-        <v>1.0266</v>
+        <v>0.8174</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.5975</v>
+        <v>-0.0605</v>
       </c>
       <c r="G18" t="n">
         <v>1.0131</v>
@@ -1858,13 +1858,13 @@
         <v>1.0267</v>
       </c>
       <c r="S18" t="n">
-        <v>0.7919</v>
+        <v>1.1196</v>
       </c>
       <c r="T18" t="n">
-        <v>0.8909</v>
+        <v>0.6817</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.09909999999999999</v>
+        <v>0.4379</v>
       </c>
       <c r="V18" t="n">
         <v>-0.3491</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.4783</v>
+        <v>0.1789</v>
       </c>
       <c r="E19" t="n">
-        <v>0.7556</v>
+        <v>0.9648</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.234</v>
+        <v>-0.7859</v>
       </c>
       <c r="G19" t="n">
         <v>-3.6162</v>
@@ -1936,13 +1936,13 @@
         <v>1.8481</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2515</v>
+        <v>0.4058</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1435</v>
+        <v>0.06569999999999999</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1079</v>
+        <v>0.3401</v>
       </c>
       <c r="V19" t="n">
         <v>1.5412</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.5693</v>
+        <v>-0.2259</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.4664</v>
+        <v>-0.1526</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.1029</v>
+        <v>-0.0733</v>
       </c>
       <c r="G20" t="n">
         <v>-0.4806</v>
@@ -2014,13 +2014,13 @@
         <v>0.616</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4645</v>
+        <v>-0.1211</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5851</v>
+        <v>-0.2713</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1206</v>
+        <v>0.1502</v>
       </c>
       <c r="V20" t="n">
         <v>-0.2402</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>G. FOLLA-CISNEROS GIMENO</t>
+          <t>P. HARGUINDEY MANEIRO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.6997</v>
+        <v>-0.9287</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.1317</v>
+        <v>-0.7145</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.5679</v>
+        <v>-0.2142</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.2498</v>
+        <v>0.0019</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.3893</v>
+        <v>-0.4349</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1395</v>
+        <v>0.4368</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1.0143</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>0.3698</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>0.6445</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.2498</v>
+        <v>-1.0124</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.3893</v>
+        <v>-0.8047</v>
       </c>
       <c r="O21" t="n">
-        <v>0.1395</v>
+        <v>-0.2077</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>-0.616</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-1.0267</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>0.4107</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2712</v>
+        <v>0.3835</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1317</v>
+        <v>-0.004</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1395</v>
+        <v>0.3875</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.1786</v>
+        <v>-0.6982</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>-0.6982</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.1786</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>P. HARGUINDEY MANEIRO</t>
+          <t>G. FOLLA-CISNEROS GIMENO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.7098</v>
+        <v>-1.5602</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.2375</v>
+        <v>-0.1317</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.4723</v>
+        <v>-1.4285</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0019</v>
+        <v>-0.2498</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.4349</v>
+        <v>-0.3893</v>
       </c>
       <c r="I22" t="n">
-        <v>0.4368</v>
+        <v>0.1395</v>
       </c>
       <c r="J22" t="n">
-        <v>1.0143</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>0.3698</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0.6445</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.0124</v>
+        <v>-0.2498</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.8047</v>
+        <v>-0.3893</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.2077</v>
+        <v>0.1395</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.616</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.0267</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.4107</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3975</v>
+        <v>-0.1317</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.527</v>
+        <v>-0.1317</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1295</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.6982</v>
+        <v>-1.1786</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.6982</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.1531</v>
+        <v>-4.4505</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.3152</v>
+        <v>-4.0014</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.8379</v>
+        <v>-0.4491</v>
       </c>
       <c r="G23" t="n">
         <v>-4.3965</v>
@@ -2248,13 +2248,13 @@
         <v>1.2321</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.9961</v>
+        <v>-0.2935</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5192</v>
+        <v>-0.2054</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4768</v>
+        <v>-0.08799999999999999</v>
       </c>
       <c r="V23" t="n">
         <v>1.0608</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.7094</v>
+        <v>-5.5699</v>
       </c>
       <c r="E24" t="n">
         <v>-3.3628</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.3466</v>
+        <v>-2.2071</v>
       </c>
       <c r="G24" t="n">
         <v>-3.3064</v>
@@ -2326,13 +2326,13 @@
         <v>0.2053</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.403</v>
+        <v>-0.2635</v>
       </c>
       <c r="T24" t="n">
         <v>-0.2635</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1395</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
         <v>-1.1786</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-10.38</v>
+        <v>-9.2432</v>
       </c>
       <c r="E25" t="n">
-        <v>-5.4181</v>
+        <v>-4.8951</v>
       </c>
       <c r="F25" t="n">
-        <v>-4.9618</v>
+        <v>-4.3481</v>
       </c>
       <c r="G25" t="n">
         <v>-5.4856</v>
@@ -2404,13 +2404,13 @@
         <v>1.6427</v>
       </c>
       <c r="S25" t="n">
-        <v>-2.2488</v>
+        <v>-1.112</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.1702</v>
+        <v>-0.6472</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.0785</v>
+        <v>-0.4648</v>
       </c>
       <c r="V25" t="n">
         <v>-2.2349</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-13.3318</v>
+        <v>-10.5424</v>
       </c>
       <c r="E26" t="n">
-        <v>1.3578</v>
+        <v>1.357699999999999</v>
       </c>
       <c r="F26" t="n">
-        <v>-14.6896</v>
+        <v>-11.9001</v>
       </c>
       <c r="G26" t="n">
         <v>-8.1959</v>
@@ -2482,13 +2482,13 @@
         <v>11.2938</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.9882000000000006</v>
+        <v>1.8013</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.1562999999999999</v>
+        <v>-0.1563000000000002</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.8316999999999999</v>
+        <v>1.9577</v>
       </c>
       <c r="V26" t="n">
         <v>-2.0944</v>
